--- a/docs/BOM_Electronics.xlsx
+++ b/docs/BOM_Electronics.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Outdoor Vehicle\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\Outdoor-Autonomous-Vehicle\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B6EADC-1CC9-417B-945A-37E9D7401E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE3C8E4-9735-4E9D-8889-D522A946501B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F0A3E672-26F2-4251-B79B-DFB5BF5737FE}"/>
   </bookViews>
@@ -701,6 +701,36 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -708,36 +738,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1093,34 +1093,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" s="1" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="18" t="s">
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="J1" s="15" t="s">
         <v>9</v>
       </c>
       <c r="K1"/>
@@ -1134,482 +1134,482 @@
       <c r="S1"/>
     </row>
     <row r="2" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="21">
+      <c r="J2" s="18">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="21">
+      <c r="J3" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="20" t="s">
+      <c r="H4" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="21">
+      <c r="J4" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="H5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="J5" s="21">
+      <c r="G5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J5" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="H6" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="J6" s="21">
+      <c r="G6" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J6" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I7" s="20" t="s">
+      <c r="H7" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I7" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="J8" s="21">
+      <c r="H8" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J8" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="A9" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="J9" s="21">
+      <c r="G9" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J9" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="G10" s="20" t="s">
+      <c r="G10" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="J10" s="21">
+      <c r="H10" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J10" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="G11" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="J11" s="21">
+      <c r="G11" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J11" s="18">
         <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I12" s="20" t="s">
+      <c r="H12" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I12" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="18">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>134</v>
-      </c>
-      <c r="I13" s="20" t="s">
+      <c r="G13" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="I13" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="I14" s="20" t="s">
+      <c r="I14" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="J14" s="21">
+      <c r="J14" s="18">
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="20" t="s">
+      <c r="I15" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="J15" s="21">
+      <c r="J15" s="18">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="G16" s="20" t="s">
+      <c r="G16" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="I16" s="20" t="s">
+      <c r="I16" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="J16" s="21">
+      <c r="J16" s="18">
         <v>5</v>
       </c>
     </row>
@@ -1624,10 +1624,10 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="126.85546875" style="15" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" style="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" style="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="126.85546875" style="12" customWidth="1"/>
+    <col min="3" max="3" width="42.5703125" style="13" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" style="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1645,7 +1645,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="63" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -1729,7 +1729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="95.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -1855,7 +1855,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="111" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -1926,24 +1926,24 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11">
+      <c r="A22" s="21">
         <v>21</v>
       </c>
-      <c r="B22" s="12" t="s">
+      <c r="B22" s="22" t="s">
         <v>122</v>
       </c>
       <c r="C22" s="8"/>
-      <c r="D22" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="126.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12"/>
+      <c r="D22" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="111" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21"/>
+      <c r="B23" s="22"/>
       <c r="C23" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="13"/>
+      <c r="D23" s="23"/>
     </row>
     <row r="24" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
